--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/156.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/156.xlsx
@@ -426,13 +426,13 @@
         <v>-3.73033083418599</v>
       </c>
       <c r="E2">
-        <v>-13.00617340397554</v>
+        <v>-13.38673730263214</v>
       </c>
       <c r="F2">
-        <v>0.3563858753567152</v>
+        <v>-0.5038455079588763</v>
       </c>
       <c r="G2">
-        <v>-6.860888284802277</v>
+        <v>-6.385116543171458</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-4.675697415091426</v>
       </c>
       <c r="E3">
-        <v>-13.32771317241616</v>
+        <v>-13.85885336030181</v>
       </c>
       <c r="F3">
-        <v>0.07823169864028036</v>
+        <v>-0.4073141977758443</v>
       </c>
       <c r="G3">
-        <v>-6.916770293505174</v>
+        <v>-6.671736954870479</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-5.730760356424837</v>
       </c>
       <c r="E4">
-        <v>-13.23669084486199</v>
+        <v>-14.40384162170291</v>
       </c>
       <c r="F4">
-        <v>0.09766685464476235</v>
+        <v>-0.2272884235950389</v>
       </c>
       <c r="G4">
-        <v>-7.26955195780653</v>
+        <v>-6.977671089245607</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-6.740442889725917</v>
       </c>
       <c r="E5">
-        <v>-14.81648070175584</v>
+        <v>-14.88353381638742</v>
       </c>
       <c r="F5">
-        <v>0.0201954500327442</v>
+        <v>-0.1464861536563639</v>
       </c>
       <c r="G5">
-        <v>-7.502236961579745</v>
+        <v>-6.70080354470528</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-7.673160152335913</v>
       </c>
       <c r="E6">
-        <v>-15.20164100153023</v>
+        <v>-16.55341766366388</v>
       </c>
       <c r="F6">
-        <v>-0.1259045371664074</v>
+        <v>0.1004824754468779</v>
       </c>
       <c r="G6">
-        <v>-6.652724491838444</v>
+        <v>-6.579733583788593</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-8.445879108296559</v>
       </c>
       <c r="E7">
-        <v>-15.15867484014546</v>
+        <v>-15.47540084071593</v>
       </c>
       <c r="F7">
-        <v>0.08932933673558534</v>
+        <v>0.3031085974782621</v>
       </c>
       <c r="G7">
-        <v>-6.729760886537285</v>
+        <v>-6.927370660321921</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-9.01616046816002</v>
       </c>
       <c r="E8">
-        <v>-16.74739484778244</v>
+        <v>-16.94746282944132</v>
       </c>
       <c r="F8">
-        <v>0.556473051298519</v>
+        <v>0.28267028854899</v>
       </c>
       <c r="G8">
-        <v>-6.152908257955898</v>
+        <v>-5.857392410392856</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-9.331918360823718</v>
       </c>
       <c r="E9">
-        <v>-16.83019799501269</v>
+        <v>-18.2926460334198</v>
       </c>
       <c r="F9">
-        <v>0.2869885678197838</v>
+        <v>0.3095276164825555</v>
       </c>
       <c r="G9">
-        <v>-5.215828548155335</v>
+        <v>-6.43938631619673</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-9.36263800271743</v>
       </c>
       <c r="E10">
-        <v>-17.8596559911764</v>
+        <v>-18.30932893166406</v>
       </c>
       <c r="F10">
-        <v>0.5273633923967415</v>
+        <v>0.08632981837004833</v>
       </c>
       <c r="G10">
-        <v>-5.794763509880923</v>
+        <v>-5.373175467091356</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-9.089540136647123</v>
       </c>
       <c r="E11">
-        <v>-17.82922011737084</v>
+        <v>-19.50204747275229</v>
       </c>
       <c r="F11">
-        <v>0.6214651009873625</v>
+        <v>0.3781951323376205</v>
       </c>
       <c r="G11">
-        <v>-5.369312060447026</v>
+        <v>-5.462576749379374</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-8.512681872457362</v>
       </c>
       <c r="E12">
-        <v>-18.49837913606227</v>
+        <v>-21.06073916924441</v>
       </c>
       <c r="F12">
-        <v>0.7461592461307721</v>
+        <v>0.5263229629388253</v>
       </c>
       <c r="G12">
-        <v>-4.763561679853341</v>
+        <v>-4.58659315750606</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-7.646421816457345</v>
       </c>
       <c r="E13">
-        <v>-20.45757360226676</v>
+        <v>-20.81846128136004</v>
       </c>
       <c r="F13">
-        <v>0.5434635412375527</v>
+        <v>0.678979478131135</v>
       </c>
       <c r="G13">
-        <v>-3.0890645722712</v>
+        <v>-3.94648262476028</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-6.523188078839343</v>
       </c>
       <c r="E14">
-        <v>-20.83678801566908</v>
+        <v>-21.66746864526609</v>
       </c>
       <c r="F14">
-        <v>0.4257666155455905</v>
+        <v>0.7278688938769591</v>
       </c>
       <c r="G14">
-        <v>-3.532277098523287</v>
+        <v>-4.108616592546086</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-5.187967097042317</v>
       </c>
       <c r="E15">
-        <v>-22.67137699107852</v>
+        <v>-21.42839238850514</v>
       </c>
       <c r="F15">
-        <v>0.5424545897409428</v>
+        <v>0.6166415176008611</v>
       </c>
       <c r="G15">
-        <v>-1.602533619317798</v>
+        <v>-1.778273929270009</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-3.694704299246022</v>
       </c>
       <c r="E16">
-        <v>-22.51994482026202</v>
+        <v>-23.98483370615926</v>
       </c>
       <c r="F16">
-        <v>1.527685785771577</v>
+        <v>1.702292380403268</v>
       </c>
       <c r="G16">
-        <v>-3.252628695729971</v>
+        <v>-2.207419947525733</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-2.104649195299099</v>
       </c>
       <c r="E17">
-        <v>-23.64610385038551</v>
+        <v>-24.78114321803805</v>
       </c>
       <c r="F17">
-        <v>1.105271425857608</v>
+        <v>1.123440836470613</v>
       </c>
       <c r="G17">
-        <v>-1.430431598913246</v>
+        <v>-1.971768694949331</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-0.4805643836843119</v>
       </c>
       <c r="E18">
-        <v>-24.54188129384279</v>
+        <v>-26.56216034593675</v>
       </c>
       <c r="F18">
-        <v>1.329581721392075</v>
+        <v>1.370032558405581</v>
       </c>
       <c r="G18">
-        <v>-1.12207745574891</v>
+        <v>-2.110934097783674</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>1.118538467711881</v>
       </c>
       <c r="E19">
-        <v>-25.60105966491883</v>
+        <v>-25.50771423019872</v>
       </c>
       <c r="F19">
-        <v>1.494179981063142</v>
+        <v>1.371664442189096</v>
       </c>
       <c r="G19">
-        <v>-0.5048725875893471</v>
+        <v>-0.5636612552757247</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>2.636963334195945</v>
       </c>
       <c r="E20">
-        <v>-25.12042554764073</v>
+        <v>-26.8303999753071</v>
       </c>
       <c r="F20">
-        <v>1.818457654767454</v>
+        <v>2.030322558442261</v>
       </c>
       <c r="G20">
-        <v>-0.1288210986924543</v>
+        <v>-0.4192453272160978</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>4.025434839609255</v>
       </c>
       <c r="E21">
-        <v>-26.34700348888432</v>
+        <v>-27.52827404768116</v>
       </c>
       <c r="F21">
-        <v>2.352340445871735</v>
+        <v>1.957124701261285</v>
       </c>
       <c r="G21">
-        <v>-0.5089412480571113</v>
+        <v>-0.8422072464044632</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>5.241905930257289</v>
       </c>
       <c r="E22">
-        <v>-25.80338282663353</v>
+        <v>-27.97120861884541</v>
       </c>
       <c r="F22">
-        <v>1.934649436888529</v>
+        <v>1.878136555934741</v>
       </c>
       <c r="G22">
-        <v>0.2559602987914965</v>
+        <v>-0.151107691262828</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>6.251577397193444</v>
       </c>
       <c r="E23">
-        <v>-27.58725289315706</v>
+        <v>-29.93810149086294</v>
       </c>
       <c r="F23">
-        <v>2.116388274858324</v>
+        <v>2.189183545481539</v>
       </c>
       <c r="G23">
-        <v>-0.3170852024197282</v>
+        <v>0.3189566698582879</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>7.030773631176029</v>
       </c>
       <c r="E24">
-        <v>-28.45461869069021</v>
+        <v>-28.6654372696433</v>
       </c>
       <c r="F24">
-        <v>2.90202517355182</v>
+        <v>2.503741156081401</v>
       </c>
       <c r="G24">
-        <v>0.5128321482746264</v>
+        <v>-0.4194903075860039</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>7.561458636775613</v>
       </c>
       <c r="E25">
-        <v>-30.12070541251124</v>
+        <v>-29.81554966303036</v>
       </c>
       <c r="F25">
-        <v>2.380968823312486</v>
+        <v>2.572682861546792</v>
       </c>
       <c r="G25">
-        <v>0.1254983201798975</v>
+        <v>0.08462963549759471</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>7.838251819111214</v>
       </c>
       <c r="E26">
-        <v>-29.5569217197413</v>
+        <v>-29.70793500671208</v>
       </c>
       <c r="F26">
-        <v>2.38761895682216</v>
+        <v>2.873572410000462</v>
       </c>
       <c r="G26">
-        <v>0.7649964020009127</v>
+        <v>-0.0499605934014754</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>7.868843503819781</v>
       </c>
       <c r="E27">
-        <v>-28.07808060542643</v>
+        <v>-30.92847422786644</v>
       </c>
       <c r="F27">
-        <v>2.660284371127646</v>
+        <v>2.777012935325735</v>
       </c>
       <c r="G27">
-        <v>0.06610051211429388</v>
+        <v>0.1215620815337041</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>7.666957856767336</v>
       </c>
       <c r="E28">
-        <v>-29.38221772099938</v>
+        <v>-30.0666626037037</v>
       </c>
       <c r="F28">
-        <v>2.760506886457552</v>
+        <v>2.253761411468983</v>
       </c>
       <c r="G28">
-        <v>-0.7163303733647548</v>
+        <v>0.01873984762948028</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>7.25619903805786</v>
       </c>
       <c r="E29">
-        <v>-27.12026759653808</v>
+        <v>-30.09727735223255</v>
       </c>
       <c r="F29">
-        <v>2.181322338828972</v>
+        <v>2.54963768040091</v>
       </c>
       <c r="G29">
-        <v>0.3948575474371584</v>
+        <v>-0.1364850116158672</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>6.66187210919778</v>
       </c>
       <c r="E30">
-        <v>-28.95559471321076</v>
+        <v>-28.69945516638892</v>
       </c>
       <c r="F30">
-        <v>2.534972263901748</v>
+        <v>2.414426582711558</v>
       </c>
       <c r="G30">
-        <v>-0.7221337596950972</v>
+        <v>-0.1478666671798815</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>5.91017364232889</v>
       </c>
       <c r="E31">
-        <v>-28.37931016794265</v>
+        <v>-29.11112968147821</v>
       </c>
       <c r="F31">
-        <v>2.556120483695219</v>
+        <v>2.317941661103083</v>
       </c>
       <c r="G31">
-        <v>-0.454443047389629</v>
+        <v>-0.8959837481443843</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>5.029286636004642</v>
       </c>
       <c r="E32">
-        <v>-29.27227995751517</v>
+        <v>-28.86421916468399</v>
       </c>
       <c r="F32">
-        <v>2.575959882992267</v>
+        <v>2.299285170457233</v>
       </c>
       <c r="G32">
-        <v>0.383671214059961</v>
+        <v>-0.5659918793353717</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>4.046495371821111</v>
       </c>
       <c r="E33">
-        <v>-28.06237132909382</v>
+        <v>-29.56552129188186</v>
       </c>
       <c r="F33">
-        <v>2.681063139059468</v>
+        <v>2.248103662107862</v>
       </c>
       <c r="G33">
-        <v>0.6212657568679149</v>
+        <v>-0.2877736322150211</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>2.989355843582081</v>
       </c>
       <c r="E34">
-        <v>-27.99833417815135</v>
+        <v>-28.70650600041886</v>
       </c>
       <c r="F34">
-        <v>2.556779864147848</v>
+        <v>2.10942170500078</v>
       </c>
       <c r="G34">
-        <v>-0.6296007013269282</v>
+        <v>-1.05103314847615</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>1.885882301865649</v>
       </c>
       <c r="E35">
-        <v>-26.40275806086676</v>
+        <v>-27.43549920068602</v>
       </c>
       <c r="F35">
-        <v>3.050019637001174</v>
+        <v>2.741136343110488</v>
       </c>
       <c r="G35">
-        <v>-1.973172366257983</v>
+        <v>-1.006807570617027</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>0.7650111179438326</v>
       </c>
       <c r="E36">
-        <v>-25.71042231220407</v>
+        <v>-28.04006859460604</v>
       </c>
       <c r="F36">
-        <v>2.767640786530462</v>
+        <v>2.441769333943164</v>
       </c>
       <c r="G36">
-        <v>-1.01215410166295</v>
+        <v>-1.871767045844567</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-0.3419601672509518</v>
       </c>
       <c r="E37">
-        <v>-26.20039867136</v>
+        <v>-27.02799541015779</v>
       </c>
       <c r="F37">
-        <v>3.036508964661514</v>
+        <v>2.535971274989524</v>
       </c>
       <c r="G37">
-        <v>-1.001656361757921</v>
+        <v>-1.217063628361679</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-1.404184576743574</v>
       </c>
       <c r="E38">
-        <v>-25.68035324479314</v>
+        <v>-27.41052466653371</v>
       </c>
       <c r="F38">
-        <v>2.488565465262114</v>
+        <v>2.930106828506723</v>
       </c>
       <c r="G38">
-        <v>-0.8758390785379192</v>
+        <v>-1.138954616908115</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-2.39329582505717</v>
       </c>
       <c r="E39">
-        <v>-25.31050371563869</v>
+        <v>-26.92756291361567</v>
       </c>
       <c r="F39">
-        <v>3.004360025758865</v>
+        <v>2.770092754042748</v>
       </c>
       <c r="G39">
-        <v>-1.273352834165907</v>
+        <v>-1.673336256766191</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-3.28762403474011</v>
       </c>
       <c r="E40">
-        <v>-24.81733478230736</v>
+        <v>-26.29359466643785</v>
       </c>
       <c r="F40">
-        <v>3.015027741172117</v>
+        <v>2.75082161478402</v>
       </c>
       <c r="G40">
-        <v>-1.322388634693592</v>
+        <v>-1.886690985135601</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-4.073094824144152</v>
       </c>
       <c r="E41">
-        <v>-21.91558373614635</v>
+        <v>-24.5978532325776</v>
       </c>
       <c r="F41">
-        <v>2.894714002854712</v>
+        <v>2.641581491907238</v>
       </c>
       <c r="G41">
-        <v>-2.795833001130255</v>
+        <v>-2.690865533716583</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-4.73885265265337</v>
       </c>
       <c r="E42">
-        <v>-23.76897040716163</v>
+        <v>-23.9314882823489</v>
       </c>
       <c r="F42">
-        <v>2.878434926654895</v>
+        <v>2.637570536942883</v>
       </c>
       <c r="G42">
-        <v>-2.456058470252696</v>
+        <v>-1.970378265822837</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-5.281045028564445</v>
       </c>
       <c r="E43">
-        <v>-20.77260595355837</v>
+        <v>-24.15091096191656</v>
       </c>
       <c r="F43">
-        <v>2.58320147082754</v>
+        <v>3.074663567234459</v>
       </c>
       <c r="G43">
-        <v>-1.965273404601281</v>
+        <v>-2.383252952753044</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-5.699491289358563</v>
       </c>
       <c r="E44">
-        <v>-23.01140651889246</v>
+        <v>-22.73553188234519</v>
       </c>
       <c r="F44">
-        <v>3.274242125590944</v>
+        <v>2.954175871762466</v>
       </c>
       <c r="G44">
-        <v>-1.976208136517494</v>
+        <v>-2.794068480357823</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-5.998408222144239</v>
       </c>
       <c r="E45">
-        <v>-20.60992505330682</v>
+        <v>-22.35647596553314</v>
       </c>
       <c r="F45">
-        <v>3.193698306281942</v>
+        <v>3.045286345661578</v>
       </c>
       <c r="G45">
-        <v>-1.891137047794842</v>
+        <v>-1.646616843718733</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-6.184341404678628</v>
       </c>
       <c r="E46">
-        <v>-20.70876805547224</v>
+        <v>-21.56800071368761</v>
       </c>
       <c r="F46">
-        <v>3.512073033873905</v>
+        <v>2.80455946493843</v>
       </c>
       <c r="G46">
-        <v>-2.114575697876873</v>
+        <v>-1.713877197440106</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-6.269018180457805</v>
       </c>
       <c r="E47">
-        <v>-18.13895415407347</v>
+        <v>-21.5359934594014</v>
       </c>
       <c r="F47">
-        <v>2.935777831746289</v>
+        <v>3.000060798938336</v>
       </c>
       <c r="G47">
-        <v>-2.489518154018109</v>
+        <v>-3.125364704109308</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-6.269315191434578</v>
       </c>
       <c r="E48">
-        <v>-17.86331499817459</v>
+        <v>-21.10644958587783</v>
       </c>
       <c r="F48">
-        <v>3.682670330276046</v>
+        <v>2.545220825409183</v>
       </c>
       <c r="G48">
-        <v>-2.746740921328402</v>
+        <v>-2.551511429786502</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-6.197603561681784</v>
       </c>
       <c r="E49">
-        <v>-18.78823770034523</v>
+        <v>-19.64353964312195</v>
       </c>
       <c r="F49">
-        <v>2.929873228899134</v>
+        <v>2.891027767912254</v>
       </c>
       <c r="G49">
-        <v>-2.46830417820246</v>
+        <v>-2.462447823143489</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-6.074055392053034</v>
       </c>
       <c r="E50">
-        <v>-15.01108281528746</v>
+        <v>-18.24654616802171</v>
       </c>
       <c r="F50">
-        <v>3.979525729478083</v>
+        <v>2.815739111406612</v>
       </c>
       <c r="G50">
-        <v>-1.910417665015558</v>
+        <v>-3.440349869988805</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-5.918749208242185</v>
       </c>
       <c r="E51">
-        <v>-17.82750382572193</v>
+        <v>-18.49947049829812</v>
       </c>
       <c r="F51">
-        <v>3.223226290722134</v>
+        <v>2.922103142660874</v>
       </c>
       <c r="G51">
-        <v>-3.39899122456669</v>
+        <v>-3.190301054862113</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-5.742462289407864</v>
       </c>
       <c r="E52">
-        <v>-16.40491088705634</v>
+        <v>-18.46322459234072</v>
       </c>
       <c r="F52">
-        <v>3.673858157845065</v>
+        <v>2.731941464939414</v>
       </c>
       <c r="G52">
-        <v>-2.69700990623747</v>
+        <v>-2.277646550050293</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-5.567253211083358</v>
       </c>
       <c r="E53">
-        <v>-15.35925001089319</v>
+        <v>-16.07589460802905</v>
       </c>
       <c r="F53">
-        <v>3.392642335207883</v>
+        <v>2.930524325677734</v>
       </c>
       <c r="G53">
-        <v>-3.052959762619909</v>
+        <v>-2.740629654262908</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-5.408270406915999</v>
       </c>
       <c r="E54">
-        <v>-14.88282737444222</v>
+        <v>-16.5686605071737</v>
       </c>
       <c r="F54">
-        <v>2.911374128059815</v>
+        <v>2.793126338044991</v>
       </c>
       <c r="G54">
-        <v>-3.781706841634136</v>
+        <v>-3.458226815900869</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-5.271549371116334</v>
       </c>
       <c r="E55">
-        <v>-13.413813048724</v>
+        <v>-16.32426329345374</v>
       </c>
       <c r="F55">
-        <v>3.232318451335261</v>
+        <v>3.323155563991449</v>
       </c>
       <c r="G55">
-        <v>-3.020109219233721</v>
+        <v>-4.20253676949521</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-5.174853332511821</v>
       </c>
       <c r="E56">
-        <v>-14.37979542472219</v>
+        <v>-14.93839627899035</v>
       </c>
       <c r="F56">
-        <v>3.668786892605126</v>
+        <v>2.685475023846779</v>
       </c>
       <c r="G56">
-        <v>-3.902349742176256</v>
+        <v>-3.839482482385496</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-5.121202124514377</v>
       </c>
       <c r="E57">
-        <v>-14.59439075099767</v>
+        <v>-13.758008772625</v>
       </c>
       <c r="F57">
-        <v>3.299313493404074</v>
+        <v>3.172803566913728</v>
       </c>
       <c r="G57">
-        <v>-3.425392825242378</v>
+        <v>-4.336153698005734</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-5.107303488459451</v>
       </c>
       <c r="E58">
-        <v>-12.37944165826197</v>
+        <v>-14.73129557719756</v>
       </c>
       <c r="F58">
-        <v>2.865076673917351</v>
+        <v>3.033452288945184</v>
       </c>
       <c r="G58">
-        <v>-3.220433640360559</v>
+        <v>-4.621426717670272</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-5.136903144486532</v>
       </c>
       <c r="E59">
-        <v>-12.68608274721736</v>
+        <v>-12.64340187969507</v>
       </c>
       <c r="F59">
-        <v>3.264353075536324</v>
+        <v>2.982201197733978</v>
       </c>
       <c r="G59">
-        <v>-5.610376054980136</v>
+        <v>-5.037300758859058</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-5.196801102499627</v>
       </c>
       <c r="E60">
-        <v>-11.76915280167026</v>
+        <v>-12.61742655278707</v>
       </c>
       <c r="F60">
-        <v>3.125303323302399</v>
+        <v>2.887947897908645</v>
       </c>
       <c r="G60">
-        <v>-5.182630397487523</v>
+        <v>-4.377038935415734</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-5.274306971445506</v>
       </c>
       <c r="E61">
-        <v>-11.50836251204253</v>
+        <v>-12.76386834524712</v>
       </c>
       <c r="F61">
-        <v>3.004429608620701</v>
+        <v>3.123295360718013</v>
       </c>
       <c r="G61">
-        <v>-4.505421891428671</v>
+        <v>-4.823873198487783</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-5.358511679663659</v>
       </c>
       <c r="E62">
-        <v>-11.96749543473222</v>
+        <v>-11.67560811409382</v>
       </c>
       <c r="F62">
-        <v>2.836186532377315</v>
+        <v>2.773169310576745</v>
       </c>
       <c r="G62">
-        <v>-4.834526534033158</v>
+        <v>-4.727933588759705</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-5.426649010050393</v>
       </c>
       <c r="E63">
-        <v>-10.99887748686157</v>
+        <v>-11.63110227154643</v>
       </c>
       <c r="F63">
-        <v>2.905171312947652</v>
+        <v>2.828244145719273</v>
       </c>
       <c r="G63">
-        <v>-3.924354938375792</v>
+        <v>-5.100962549579243</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-5.463734439337882</v>
       </c>
       <c r="E64">
-        <v>-11.49277097603412</v>
+        <v>-10.73630750694882</v>
       </c>
       <c r="F64">
-        <v>3.67160499850945</v>
+        <v>2.483106524077665</v>
       </c>
       <c r="G64">
-        <v>-4.706186615112232</v>
+        <v>-5.261831888969048</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-5.45447223828685</v>
       </c>
       <c r="E65">
-        <v>-10.12678849093842</v>
+        <v>-11.83474321919736</v>
       </c>
       <c r="F65">
-        <v>3.468101635398501</v>
+        <v>2.897429391201088</v>
       </c>
       <c r="G65">
-        <v>-4.912781209490451</v>
+        <v>-5.413958077589637</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-5.379427317656502</v>
       </c>
       <c r="E66">
-        <v>-10.09491256239842</v>
+        <v>-12.22280174233666</v>
       </c>
       <c r="F66">
-        <v>2.611400753953641</v>
+        <v>2.427408756648232</v>
       </c>
       <c r="G66">
-        <v>-4.8064497973146</v>
+        <v>-5.06218281913222</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-5.229946744935585</v>
       </c>
       <c r="E67">
-        <v>-8.719633120164968</v>
+        <v>-10.86758796843119</v>
       </c>
       <c r="F67">
-        <v>3.226122263162321</v>
+        <v>2.214679037404902</v>
       </c>
       <c r="G67">
-        <v>-4.81598747901324</v>
+        <v>-5.336342337421424</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-4.997199760251516</v>
       </c>
       <c r="E68">
-        <v>-10.5251130646531</v>
+        <v>-11.0206820892085</v>
       </c>
       <c r="F68">
-        <v>2.995352358620823</v>
+        <v>2.16779344240645</v>
       </c>
       <c r="G68">
-        <v>-5.073799523429523</v>
+        <v>-4.882867119997596</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-4.673816447870991</v>
       </c>
       <c r="E69">
-        <v>-10.03836097899064</v>
+        <v>-11.08145421039143</v>
       </c>
       <c r="F69">
-        <v>2.610028977534605</v>
+        <v>2.209939119126083</v>
       </c>
       <c r="G69">
-        <v>-4.487296654601161</v>
+        <v>-5.216182776528037</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-4.262455487163597</v>
       </c>
       <c r="E70">
-        <v>-9.79002852135801</v>
+        <v>-10.41182875887722</v>
       </c>
       <c r="F70">
-        <v>2.795450736977247</v>
+        <v>2.0741564479288</v>
       </c>
       <c r="G70">
-        <v>-4.747313522346598</v>
+        <v>-6.158810960652419</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-3.766001700590837</v>
       </c>
       <c r="E71">
-        <v>-9.829774937723332</v>
+        <v>-9.528029129170234</v>
       </c>
       <c r="F71">
-        <v>2.293160221880933</v>
+        <v>2.109368689487001</v>
       </c>
       <c r="G71">
-        <v>-5.645815444978034</v>
+        <v>-4.886929159374282</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-3.190696094879976</v>
       </c>
       <c r="E72">
-        <v>-10.25916937160464</v>
+        <v>-11.09940055288383</v>
       </c>
       <c r="F72">
-        <v>2.760379317877521</v>
+        <v>1.696707527373594</v>
       </c>
       <c r="G72">
-        <v>-4.884353554944729</v>
+        <v>-5.80454617194947</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-2.549829063871431</v>
       </c>
       <c r="E73">
-        <v>-9.92753563460092</v>
+        <v>-11.33302905541355</v>
       </c>
       <c r="F73">
-        <v>1.957941471520446</v>
+        <v>1.686735640578693</v>
       </c>
       <c r="G73">
-        <v>-3.936070959039272</v>
+        <v>-5.468366893527559</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-1.856463034130581</v>
       </c>
       <c r="E74">
-        <v>-10.41319635802754</v>
+        <v>-10.86477125759841</v>
       </c>
       <c r="F74">
-        <v>1.935267398971018</v>
+        <v>1.681631240642643</v>
       </c>
       <c r="G74">
-        <v>-4.766905330848005</v>
+        <v>-5.152040956704658</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-1.126156776655782</v>
       </c>
       <c r="E75">
-        <v>-11.23207578436056</v>
+        <v>-10.67686222865013</v>
       </c>
       <c r="F75">
-        <v>2.029267218371094</v>
+        <v>1.726374677537455</v>
       </c>
       <c r="G75">
-        <v>-4.436400327480405</v>
+        <v>-5.561495850092797</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-0.3764314440972309</v>
       </c>
       <c r="E76">
-        <v>-10.28655305392903</v>
+        <v>-11.0356803951219</v>
       </c>
       <c r="F76">
-        <v>2.284300004140589</v>
+        <v>1.911834541880625</v>
       </c>
       <c r="G76">
-        <v>-4.592174737285272</v>
+        <v>-5.08021867123017</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>0.3750824375234007</v>
       </c>
       <c r="E77">
-        <v>-12.03247450826828</v>
+        <v>-11.81076494932675</v>
       </c>
       <c r="F77">
-        <v>1.306299627168992</v>
+        <v>1.217959213864842</v>
       </c>
       <c r="G77">
-        <v>-3.791353771335572</v>
+        <v>-4.720345818383695</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>1.113014513633205</v>
       </c>
       <c r="E78">
-        <v>-11.40716923186713</v>
+        <v>-11.82426885881762</v>
       </c>
       <c r="F78">
-        <v>1.594647693144278</v>
+        <v>1.38987527117224</v>
       </c>
       <c r="G78">
-        <v>-4.49502346788982</v>
+        <v>-4.58237221194349</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>1.824187244193349</v>
       </c>
       <c r="E79">
-        <v>-11.84377299636865</v>
+        <v>-12.38827218257693</v>
       </c>
       <c r="F79">
-        <v>1.488381409243546</v>
+        <v>1.155036425948191</v>
       </c>
       <c r="G79">
-        <v>-3.299751000935958</v>
+        <v>-3.79472059614901</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>2.495583615240642</v>
       </c>
       <c r="E80">
-        <v>-13.52664450709911</v>
+        <v>-13.8449735874683</v>
       </c>
       <c r="F80">
-        <v>1.138661259129651</v>
+        <v>1.446015386794768</v>
       </c>
       <c r="G80">
-        <v>-2.902184276579341</v>
+        <v>-3.991323964089708</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>3.12085821620858</v>
       </c>
       <c r="E81">
-        <v>-14.02277959090547</v>
+        <v>-13.64347913649701</v>
       </c>
       <c r="F81">
-        <v>1.288638834141307</v>
+        <v>1.202470400167297</v>
       </c>
       <c r="G81">
-        <v>-3.383461455441969</v>
+        <v>-3.198905162718679</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>3.694682199861444</v>
       </c>
       <c r="E82">
-        <v>-16.2435975859551</v>
+        <v>-13.38504365335327</v>
       </c>
       <c r="F82">
-        <v>2.132064299588902</v>
+        <v>1.208863739782103</v>
       </c>
       <c r="G82">
-        <v>-2.986431039462714</v>
+        <v>-2.961552289735092</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>4.211303176552414</v>
       </c>
       <c r="E83">
-        <v>-15.46387587436641</v>
+        <v>-15.41231919778908</v>
       </c>
       <c r="F83">
-        <v>1.297214093495087</v>
+        <v>1.013012834738216</v>
       </c>
       <c r="G83">
-        <v>-2.451188657764428</v>
+        <v>-2.176658358374825</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>4.668618025156697</v>
       </c>
       <c r="E84">
-        <v>-16.31474896956362</v>
+        <v>-17.79639320928924</v>
       </c>
       <c r="F84">
-        <v>1.311457042618822</v>
+        <v>0.71073080068044</v>
       </c>
       <c r="G84">
-        <v>-2.438019307609207</v>
+        <v>-2.751723292365005</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>5.063336536691827</v>
       </c>
       <c r="E85">
-        <v>-18.03745293766555</v>
+        <v>-17.55660145363508</v>
       </c>
       <c r="F85">
-        <v>1.002094952369319</v>
+        <v>0.4485500325921881</v>
       </c>
       <c r="G85">
-        <v>-2.863758774505021</v>
+        <v>-2.38753679868086</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>5.391129479443017</v>
       </c>
       <c r="E86">
-        <v>-17.98627665290487</v>
+        <v>-18.26060707981553</v>
       </c>
       <c r="F86">
-        <v>0.6734849171483659</v>
+        <v>0.3539206539659838</v>
       </c>
       <c r="G86">
-        <v>-2.670277251007855</v>
+        <v>-2.38013441885505</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>5.650385892541411</v>
       </c>
       <c r="E87">
-        <v>-20.90916208725967</v>
+        <v>-20.13373336903024</v>
       </c>
       <c r="F87">
-        <v>0.5772418788215081</v>
+        <v>0.4036467207886353</v>
       </c>
       <c r="G87">
-        <v>-1.311384381321054</v>
+        <v>-2.007691424595963</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>5.83596869059342</v>
       </c>
       <c r="E88">
-        <v>-20.10646742703006</v>
+        <v>-21.70489648293949</v>
       </c>
       <c r="F88">
-        <v>0.5348029600412839</v>
+        <v>0.2964783447862549</v>
       </c>
       <c r="G88">
-        <v>-1.718283533552876</v>
+        <v>-1.644061102562416</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>5.943539352191896</v>
       </c>
       <c r="E89">
-        <v>-22.20104062369386</v>
+        <v>-23.77802735517697</v>
       </c>
       <c r="F89">
-        <v>0.07270234622659366</v>
+        <v>-0.04841905030854166</v>
       </c>
       <c r="G89">
-        <v>-0.6734819824499678</v>
+        <v>-1.93053253971217</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>5.97131503364425</v>
       </c>
       <c r="E90">
-        <v>-24.20836824012588</v>
+        <v>-23.80686467765781</v>
       </c>
       <c r="F90">
-        <v>0.3761184152588022</v>
+        <v>-0.3298527335726597</v>
       </c>
       <c r="G90">
-        <v>-2.575860492227841</v>
+        <v>-1.058885762495302</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>5.913684995096617</v>
       </c>
       <c r="E91">
-        <v>-25.79931172850063</v>
+        <v>-25.55687081555199</v>
       </c>
       <c r="F91">
-        <v>0.2902009766078403</v>
+        <v>0.06382638950559695</v>
       </c>
       <c r="G91">
-        <v>-2.523414829794707</v>
+        <v>-2.447192829298527</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>5.76887163237039</v>
       </c>
       <c r="E92">
-        <v>-28.37167516076572</v>
+        <v>-26.66894629151163</v>
       </c>
       <c r="F92">
-        <v>-0.3582615936516687</v>
+        <v>-0.9500712888663168</v>
       </c>
       <c r="G92">
-        <v>-2.116446156106561</v>
+        <v>-2.25776341354143</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>5.536396489559053</v>
       </c>
       <c r="E93">
-        <v>-28.62736638866081</v>
+        <v>-28.29675155830881</v>
       </c>
       <c r="F93">
-        <v>-0.7343760143209647</v>
+        <v>-0.9482033203730038</v>
       </c>
       <c r="G93">
-        <v>-1.697566139568117</v>
+        <v>-2.454125111657761</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>5.212894587686854</v>
       </c>
       <c r="E94">
-        <v>-31.81377504670697</v>
+        <v>-30.85391969604116</v>
       </c>
       <c r="F94">
-        <v>-0.7297313582934678</v>
+        <v>-0.9943268173608804</v>
       </c>
       <c r="G94">
-        <v>-2.120974982404284</v>
+        <v>-2.312960139317699</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>4.805019481583871</v>
       </c>
       <c r="E95">
-        <v>-32.93345156628848</v>
+        <v>-32.81651731046242</v>
       </c>
       <c r="F95">
-        <v>-0.4262804978303417</v>
+        <v>-1.254940314323036</v>
       </c>
       <c r="G95">
-        <v>-1.786904521490889</v>
+        <v>-2.782319354238949</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>4.314866989205177</v>
       </c>
       <c r="E96">
-        <v>-35.97491282829713</v>
+        <v>-35.99608118004598</v>
       </c>
       <c r="F96">
-        <v>-1.106588824523075</v>
+        <v>-1.408881627357087</v>
       </c>
       <c r="G96">
-        <v>-1.715098788744097</v>
+        <v>-2.53098935798856</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>3.75612416275345</v>
       </c>
       <c r="E97">
-        <v>-37.8444706799938</v>
+        <v>-37.72136411409528</v>
       </c>
       <c r="F97">
-        <v>-1.336051565302955</v>
+        <v>-1.535813192855458</v>
       </c>
       <c r="G97">
-        <v>-2.573241850706278</v>
+        <v>-2.647616566791544</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>3.133814601849041</v>
       </c>
       <c r="E98">
-        <v>-39.72336398085728</v>
+        <v>-40.18194216548103</v>
       </c>
       <c r="F98">
-        <v>-1.370191071074531</v>
+        <v>-1.791884751348064</v>
       </c>
       <c r="G98">
-        <v>-2.493120027564836</v>
+        <v>-3.239518935394458</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>2.485861540586054</v>
       </c>
       <c r="E99">
-        <v>-43.45212759266908</v>
+        <v>-41.52747179772109</v>
       </c>
       <c r="F99">
-        <v>-1.681487399209571</v>
+        <v>-2.006060800076682</v>
       </c>
       <c r="G99">
-        <v>-2.38331254257275</v>
+        <v>-3.894732176890393</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>1.796881718300859</v>
       </c>
       <c r="E100">
-        <v>-44.10362329849359</v>
+        <v>-44.21368559501301</v>
       </c>
       <c r="F100">
-        <v>-1.769114588179911</v>
+        <v>-2.212020272536931</v>
       </c>
       <c r="G100">
-        <v>-3.979740365247799</v>
+        <v>-3.985609962488927</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>1.147483219296926</v>
       </c>
       <c r="E101">
-        <v>-47.08920771972159</v>
+        <v>-46.16952899045183</v>
       </c>
       <c r="F101">
-        <v>-1.363631229611761</v>
+        <v>-1.891401497650785</v>
       </c>
       <c r="G101">
-        <v>-3.343854088610128</v>
+        <v>-3.983021115877217</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>0.4708676348091931</v>
       </c>
       <c r="E102">
-        <v>-47.94028459624915</v>
+        <v>-48.0203117889127</v>
       </c>
       <c r="F102">
-        <v>-2.086578939996196</v>
+        <v>-2.343835892242208</v>
       </c>
       <c r="G102">
-        <v>-3.821231444827494</v>
+        <v>-4.088044862565056</v>
       </c>
     </row>
   </sheetData>
